--- a/data/trans_bre/P13_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P13_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,7</t>
+          <t>-1,36; 1,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,14</t>
+          <t>3,0; 9,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,08</t>
+          <t>-0,01; 4,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,74</t>
+          <t>-1,77; 2,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,43; 135,51</t>
+          <t>-53,66; 126,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,01; 239,86</t>
+          <t>45,43; 222,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 193,63</t>
+          <t>0,13; 174,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 56,31</t>
+          <t>-22,83; 56,93</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,14</t>
+          <t>-1,59; 2,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,46</t>
+          <t>1,07; 5,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,51</t>
+          <t>0,2; 3,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,55</t>
+          <t>2,3; 6,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 69,18</t>
+          <t>-31,59; 71,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,37; 139,19</t>
+          <t>18,37; 147,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 168,94</t>
+          <t>3,59; 172,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,61; 334,53</t>
+          <t>52,17; 382,22</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,45</t>
+          <t>-0,1; 4,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,21</t>
+          <t>2,02; 7,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,65</t>
+          <t>-0,78; 3,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,53</t>
+          <t>-3,79; 2,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 194,57</t>
+          <t>-3,05; 183,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,17; 254,73</t>
+          <t>34,99; 239,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 135,07</t>
+          <t>-18,29; 138,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,66; 56,33</t>
+          <t>-54,25; 55,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,57</t>
+          <t>1,81; 5,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,8</t>
+          <t>2,85; 7,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,36</t>
+          <t>0,5; 4,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,81</t>
+          <t>-0,18; 4,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,62; 232,99</t>
+          <t>40,2; 228,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,08; 204,27</t>
+          <t>49,03; 211,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 150,81</t>
+          <t>9,2; 156,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 77,21</t>
+          <t>-3,23; 81,59</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,56</t>
+          <t>0,74; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,89</t>
+          <t>3,34; 5,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,12</t>
+          <t>1,03; 3,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,3</t>
+          <t>0,57; 3,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,35; 93,65</t>
+          <t>18,12; 96,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,16; 146,34</t>
+          <t>63,41; 143,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,09; 103,33</t>
+          <t>25,67; 101,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,92; 83,86</t>
+          <t>11,1; 85,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P13_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P13_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,55</t>
+          <t>-1,18; 1,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,13</t>
+          <t>3,16; 8,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,93</t>
+          <t>0,21; 5,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,77</t>
+          <t>-1,75; 2,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,66; 126,67</t>
+          <t>-49,58; 146,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,43; 222,66</t>
+          <t>45,59; 234,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 174,2</t>
+          <t>3,13; 178,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 56,93</t>
+          <t>-21,9; 61,52</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>135,27%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,19</t>
+          <t>-1,78; 2,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,68</t>
+          <t>1,18; 5,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,53</t>
+          <t>0,31; 3,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,74</t>
+          <t>1,86; 5,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 71,23</t>
+          <t>-35,14; 72,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,37; 147,79</t>
+          <t>17,89; 134,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 172,69</t>
+          <t>7,1; 183,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,17; 382,22</t>
+          <t>39,43; 183,55</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,66%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 4,36</t>
+          <t>-0,3; 4,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 7,31</t>
+          <t>1,95; 7,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,75</t>
+          <t>-0,47; 3,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,45</t>
+          <t>-1,33; 3,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 183,0</t>
+          <t>-7,83; 187,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,99; 239,8</t>
+          <t>34,59; 234,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 138,2</t>
+          <t>-12,83; 152,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,25; 55,98</t>
+          <t>-18,64; 71,71</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,73</t>
+          <t>1,63; 5,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,73</t>
+          <t>2,72; 7,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,71</t>
+          <t>0,37; 4,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,0</t>
+          <t>0,85; 4,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,2; 228,64</t>
+          <t>35,78; 232,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,03; 211,3</t>
+          <t>45,47; 194,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 156,75</t>
+          <t>7,22; 164,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 81,59</t>
+          <t>13,42; 99,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,69</t>
+          <t>0,58; 2,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,95</t>
+          <t>3,53; 5,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,12</t>
+          <t>1,05; 3,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,37</t>
+          <t>1,12; 3,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,12; 96,14</t>
+          <t>15,73; 94,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,41; 143,83</t>
+          <t>68,32; 146,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,67; 101,19</t>
+          <t>26,24; 105,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,1; 85,35</t>
+          <t>19,21; 70,13</t>
         </is>
       </c>
     </row>
